--- a/longmemeval_experiment/experiment_results.xlsx
+++ b/longmemeval_experiment/experiment_results.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1992,6 +1992,652 @@
         <v>97262</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>letta-letta_cost</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Letta</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>ollama/bge-m3:latest</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>partial (22)</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0.1709977965916331</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0.1704545454545454</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0.08637512614856953</v>
+      </c>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+      <c r="Y18" s="5" t="n">
+        <v>24841255</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>partial (5)</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0.1434343434343434</v>
+      </c>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.9839441578296375</v>
+      </c>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+      <c r="Y19" s="5" t="n">
+        <v>3747229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>partial (5)</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0.1205454545454545</v>
+      </c>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+      <c r="Y20" s="5" t="n">
+        <v>3308935</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>partial (5)</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.08988380041011619</v>
+      </c>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n">
+        <v>3273551</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>partial (5)</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0.0991274978891078</v>
+      </c>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <v>0.9839441578296375</v>
+      </c>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+      <c r="Y22" s="5" t="n">
+        <v>3072591</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>partial (5)</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0.0829059829059829</v>
+      </c>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0.9839441578296375</v>
+      </c>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+      <c r="Y23" s="5" t="n">
+        <v>3184952</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>structmem-sm_31b</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>partial (18)</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+      <c r="Y24" s="5" t="n">
+        <v>7608661</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>structmem-sm_cost</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>partial (22)</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0.05454545454545454</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>0.1590909090909091</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>0.1590909090909091</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0.1590909090909091</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <v>0.1642339633075208</v>
+      </c>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+      <c r="Y25" s="5" t="n">
+        <v>9350486</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
